--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/MISSISSIPPI_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/MISSISSIPPI_2019.xlsx
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C80">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C158">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C357">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C370">
